--- a/survey_templates/040_third_party_application_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/040_third_party_application_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -807,8 +807,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -870,12 +870,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option':_'login'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option': 'login'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option':_'settings'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option': 'settings'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option':_'chat'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option': 'chat'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option':_'ui'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option': 'ui'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option':_'speed'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option': 'speed'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option':_'reliability'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option': 'reliability'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option':_'1_-_unsatisfactory'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option': '1 - Unsatisfactory'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option':_'2_-_satisfactory'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option': '2 - Satisfactory'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option':_'3_-_satisfactory'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option': '3 - Satisfactory'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option':_'4_-_satisfactory'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option': '4 - Satisfactory'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option':_'5_-_satisfactory'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option': '5 - Satisfactory'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option':_'ui'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option': 'ui'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option':_'navigation'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option': 'navigation'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option':_'layout'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option': 'layout'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
